--- a/data/trans_orig/Q20C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007 (tasa de respuesta: 96,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>801</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012 (tasa de respuesta: 97,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6203,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -6772,12 +6772,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -7228,12 +7228,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7313,12 +7313,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>12189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -8058,12 +8058,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8221,12 +8221,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -8479,12 +8479,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -8592,12 +8592,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8677,12 +8677,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -8705,12 +8705,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -9048,12 +9048,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -9161,12 +9161,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -9617,12 +9617,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -9843,12 +9843,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>13890</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -10412,12 +10412,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>44475</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -10755,12 +10755,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10805,12 +10805,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -10868,12 +10868,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -10981,12 +10981,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>63987</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016 (tasa de respuesta: 92,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11447,12 +11447,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12066,12 +12066,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12179,12 +12179,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -12585,12 +12585,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12670,12 +12670,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12826,12 +12826,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12861,12 +12861,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12896,12 +12896,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12959,12 +12959,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12974,12 +12974,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12994,12 +12994,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13239,12 +13239,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -13267,12 +13267,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13352,12 +13352,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13395,12 +13395,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13450,12 +13450,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -13493,12 +13493,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,86%</t>
         </is>
       </c>
     </row>
@@ -13836,12 +13836,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13921,12 +13921,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13984,12 +13984,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13999,12 +13999,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14147,12 +14147,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -14292,12 +14292,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14475,12 +14475,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14490,12 +14490,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -14701,12 +14701,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14716,12 +14716,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>838</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -14974,12 +14974,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15044,12 +15044,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15059,12 +15059,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -15087,12 +15087,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15157,12 +15157,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -15205,7 +15205,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15578,12 +15578,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15593,12 +15593,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15613,12 +15613,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10812</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15628,12 +15628,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -15656,12 +15656,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15671,12 +15671,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15691,12 +15691,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15706,12 +15706,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15741,12 +15741,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15839,12 +15839,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -16112,12 +16112,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16162,12 +16162,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -16225,12 +16225,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16240,12 +16240,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16310,12 +16310,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -16338,12 +16338,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16373,12 +16373,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16388,12 +16388,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16408,12 +16408,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16423,12 +16423,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023 (tasa de respuesta: 93,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -16844,7 +16844,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -16879,7 +16879,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -16952,12 +16952,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -16967,12 +16967,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -16992,7 +16992,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -17030,12 +17030,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -17045,12 +17045,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -17143,12 +17143,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -17178,12 +17178,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -17193,12 +17193,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -17213,12 +17213,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -17228,12 +17228,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -17373,12 +17373,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -17428,7 +17428,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -17443,12 +17443,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -17458,12 +17458,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -17486,12 +17486,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -17501,12 +17501,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -17649,12 +17649,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -17669,12 +17669,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -17684,12 +17684,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -17712,12 +17712,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -17727,12 +17727,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -17747,12 +17747,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -17762,12 +17762,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -17782,12 +17782,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -17797,12 +17797,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -17947,7 +17947,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -18012,12 +18012,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -18027,12 +18027,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -18055,12 +18055,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -18070,12 +18070,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -18125,12 +18125,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -18140,12 +18140,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -18238,12 +18238,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -18253,12 +18253,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -18281,12 +18281,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,35%</t>
         </is>
       </c>
     </row>
@@ -18511,12 +18511,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -18526,12 +18526,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -18546,12 +18546,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18581,12 +18581,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -18596,12 +18596,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -18659,12 +18659,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -18674,12 +18674,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18694,12 +18694,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18709,12 +18709,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -18737,12 +18737,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -18752,12 +18752,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -18807,12 +18807,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -18822,12 +18822,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -18885,12 +18885,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -18900,12 +18900,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -18920,12 +18920,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -18935,12 +18935,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19155,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -19170,7 +19170,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -19341,12 +19341,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -19356,12 +19356,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -19649,12 +19649,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -19664,12 +19664,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -19689,7 +19689,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -19719,12 +19719,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -19734,12 +19734,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,77%</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -19797,12 +19797,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>823</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -19812,12 +19812,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -19832,12 +19832,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -19847,12 +19847,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,49%</t>
         </is>
       </c>
     </row>
@@ -19880,7 +19880,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -19910,12 +19910,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -19925,12 +19925,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20058,12 +20058,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>419</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -20073,12 +20073,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -20253,12 +20253,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -20288,12 +20288,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -20303,12 +20303,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -20366,12 +20366,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -20381,12 +20381,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -20401,12 +20401,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -20416,12 +20416,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -20444,12 +20444,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>356</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -20459,12 +20459,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20514,12 +20514,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -20529,12 +20529,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -20557,12 +20557,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -20572,12 +20572,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20592,12 +20592,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -20607,12 +20607,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20627,12 +20627,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20642,12 +20642,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>61,72%</t>
         </is>
       </c>
     </row>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -20822,12 +20822,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -20837,12 +20837,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -20905,7 +20905,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -20970,12 +20970,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -20985,12 +20985,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -21161,12 +21161,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>751</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -21176,12 +21176,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -21196,12 +21196,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -21211,12 +21211,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -21356,12 +21356,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -21371,12 +21371,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -21406,12 +21406,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21426,12 +21426,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -21469,12 +21469,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -21484,12 +21484,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21519,12 +21519,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21539,12 +21539,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21554,12 +21554,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -21582,12 +21582,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21597,12 +21597,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21617,12 +21617,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21632,12 +21632,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21652,12 +21652,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21667,12 +21667,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -21695,12 +21695,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -21710,12 +21710,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21730,12 +21730,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -21745,12 +21745,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21765,12 +21765,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>32955</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>50185</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -21780,12 +21780,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
